--- a/planilhas/equipment.xlsx
+++ b/planilhas/equipment.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="1869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="1877">
   <si>
     <t xml:space="preserve">Model Name</t>
   </si>
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Vy</t>
   </si>
   <si>
-    <t xml:space="preserve">LarguraMetros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ComprimentoMetros</t>
+    <t xml:space="preserve">Vx_largura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vy_altura</t>
   </si>
   <si>
     <t xml:space="preserve">ARGO_PARNAIBAIII_V2_LD::ECHO_FOX::REATOR1</t>
@@ -5581,6 +5581,18 @@
     <t xml:space="preserve">[[-41.764294096417586, -3.123543183817039], [-41.764294096417586, NaN]]</t>
   </si>
   <si>
+    <t xml:space="preserve">ARGO_PARNAIBAIII_V2_LD::BASE::canaleta9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-41.764725924901775, -3.1229457840766752]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.764725924901775, -3.1229457840766752], [NaN, -3.1229457840766752]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.764725924901775, -3.1229457840766752], [-41.764725924901775, NaN]]</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARGO_PARNAIBAIII_V2_LD::BASE::talude1</t>
   </si>
   <si>
@@ -5620,13 +5632,25 @@
     <t xml:space="preserve">ARGO_PARNAIBAIII_V2_LD::BASE::talude4</t>
   </si>
   <si>
-    <t xml:space="preserve">[-41.7635473934309, -3.122882479648937]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[[-41.7635473934309, -3.122882479648937], [100.00089885919243, -3.122882479648937]]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[[-41.7635473934309, -3.122882479648937], [-41.7635473934309, 2.0000180869207522]]</t>
+    <t xml:space="preserve">[-41.763457429197345, -3.12288247955997]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.763457429197345, -3.12288247955997], [100.00089885919243, -3.12288247955997]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.763457429197345, -3.12288247955997], [-41.763457429197345, 2.0000180869207522]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGO_PARNAIBAIII_V2_LD::BASE::talude5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-41.76514060201819, -3.1237367607723403]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.76514060201819, -3.1237367607723403], [75.00067414439432, -3.1237367607723403]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.76514060201819, -3.1237367607723403], [-41.76514060201819, 2.000018087029065]]</t>
   </si>
 </sst>
 </file>
@@ -5748,6 +5772,9 @@
   </sheetPr>
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.69"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -19152,10 +19179,10 @@
         <v>1853</v>
       </c>
       <c r="B463" s="2" t="n">
-        <v>-3.1223398743864</v>
+        <v>-3.12294578407668</v>
       </c>
       <c r="C463" s="2" t="n">
-        <v>-41.7652036328292</v>
+        <v>-41.7647259249018</v>
       </c>
       <c r="D463" s="2" t="n">
         <v>77</v>
@@ -19170,10 +19197,10 @@
         <v>1856</v>
       </c>
       <c r="H463" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="I463" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I463" s="2" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19181,10 +19208,10 @@
         <v>1857</v>
       </c>
       <c r="B464" s="2" t="n">
-        <v>-3.12254787337271</v>
+        <v>-3.1223398743864</v>
       </c>
       <c r="C464" s="2" t="n">
-        <v>-41.7644020536924</v>
+        <v>-41.7652036328292</v>
       </c>
       <c r="D464" s="2" t="n">
         <v>77</v>
@@ -19199,10 +19226,10 @@
         <v>1860</v>
       </c>
       <c r="H464" s="2" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19210,10 +19237,10 @@
         <v>1861</v>
       </c>
       <c r="B465" s="2" t="n">
-        <v>-3.1234002758931</v>
+        <v>-3.12254787337271</v>
       </c>
       <c r="C465" s="2" t="n">
-        <v>-41.7644470357224</v>
+        <v>-41.7644020536924</v>
       </c>
       <c r="D465" s="2" t="n">
         <v>77</v>
@@ -19228,7 +19255,7 @@
         <v>1864</v>
       </c>
       <c r="H465" s="2" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="I465" s="2" t="n">
         <v>2</v>
@@ -19239,10 +19266,10 @@
         <v>1865</v>
       </c>
       <c r="B466" s="2" t="n">
-        <v>-3.12288247964894</v>
+        <v>-3.1234002758931</v>
       </c>
       <c r="C466" s="2" t="n">
-        <v>-41.7635473934309</v>
+        <v>-41.7644470357224</v>
       </c>
       <c r="D466" s="2" t="n">
         <v>77</v>
@@ -19257,10 +19284,68 @@
         <v>1868</v>
       </c>
       <c r="H466" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="I466" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I466" s="2" t="n">
+    </row>
+    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B467" s="2" t="n">
+        <v>-3.12288247955997</v>
+      </c>
+      <c r="C467" s="2" t="n">
+        <v>-41.7634574291974</v>
+      </c>
+      <c r="D467" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F467" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="G467" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" s="2" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B468" s="2" t="n">
+        <v>-3.12373676077234</v>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>-41.7651406020182</v>
+      </c>
+      <c r="D468" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F468" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G468" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" s="2" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/planilhas/equipment.xlsx
+++ b/planilhas/equipment.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="2963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="2971">
   <si>
     <t xml:space="preserve">Model Name</t>
   </si>
@@ -8321,6 +8321,30 @@
   </si>
   <si>
     <t xml:space="preserve">[[-41.7657583333333, -3.12352777777778], [-41.7657583333333, -3.1235121416594342]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ls_diversos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-41.765903, -3.123187]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.765903, -3.123187], [-41.76547117180943, -3.123187]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.765903, -3.123187], [-41.765903, -3.1225630035680925]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_svc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-41.765774, -3.122447]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.765774, -3.122447], [-41.76503179566388, -3.122447]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[-41.765774, -3.122447], [-41.765774, -3.122040949937832]]</t>
   </si>
   <si>
     <t xml:space="preserve">b_canaleta1deitado</t>
@@ -9024,7 +9048,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I740"/>
+  <dimension ref="A1:I742"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29071,10 +29095,10 @@
         <v>2767</v>
       </c>
       <c r="B692" s="0" t="n">
-        <v>-3.12237361111111</v>
+        <v>-3.123187</v>
       </c>
       <c r="C692" s="0" t="n">
-        <v>-41.7646361111111</v>
+        <v>-41.765903</v>
       </c>
       <c r="D692" s="0" t="n">
         <v>77</v>
@@ -29089,10 +29113,10 @@
         <v>2770</v>
       </c>
       <c r="H692" s="0" t="n">
-        <v>98.6936879523502</v>
+        <v>69</v>
       </c>
       <c r="I692" s="0" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29100,10 +29124,10 @@
         <v>2771</v>
       </c>
       <c r="B693" s="0" t="n">
-        <v>-3.12244444444444</v>
+        <v>-3.122447</v>
       </c>
       <c r="C693" s="0" t="n">
-        <v>-41.7649694444445</v>
+        <v>-41.765774</v>
       </c>
       <c r="D693" s="0" t="n">
         <v>77</v>
@@ -29118,10 +29142,10 @@
         <v>2774</v>
       </c>
       <c r="H693" s="0" t="n">
-        <v>1</v>
+        <v>44.9</v>
       </c>
       <c r="I693" s="0" t="n">
-        <v>16.0614894048131</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29129,10 +29153,10 @@
         <v>2775</v>
       </c>
       <c r="B694" s="0" t="n">
-        <v>-3.12229305555555</v>
+        <v>-3.12237361111111</v>
       </c>
       <c r="C694" s="0" t="n">
-        <v>-41.764675</v>
+        <v>-41.7646361111111</v>
       </c>
       <c r="D694" s="0" t="n">
         <v>77</v>
@@ -29147,10 +29171,10 @@
         <v>2778</v>
       </c>
       <c r="H694" s="0" t="n">
-        <v>1</v>
+        <v>98.6936879523502</v>
       </c>
       <c r="I694" s="0" t="n">
-        <v>17.6058633850347</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29158,10 +29182,10 @@
         <v>2779</v>
       </c>
       <c r="B695" s="0" t="n">
-        <v>-3.12229305555555</v>
+        <v>-3.12244444444444</v>
       </c>
       <c r="C695" s="0" t="n">
-        <v>-41.7643652777778</v>
+        <v>-41.7649694444445</v>
       </c>
       <c r="D695" s="0" t="n">
         <v>77</v>
@@ -29179,7 +29203,7 @@
         <v>1</v>
       </c>
       <c r="I695" s="0" t="n">
-        <v>17.6085645678712</v>
+        <v>16.0614894048131</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29187,10 +29211,10 @@
         <v>2783</v>
       </c>
       <c r="B696" s="0" t="n">
-        <v>-3.12243888888889</v>
+        <v>-3.12229305555555</v>
       </c>
       <c r="C696" s="0" t="n">
-        <v>-41.7643208333334</v>
+        <v>-41.764675</v>
       </c>
       <c r="D696" s="0" t="n">
         <v>77</v>
@@ -29205,10 +29229,10 @@
         <v>2786</v>
       </c>
       <c r="H696" s="0" t="n">
-        <v>174.256273563526</v>
+        <v>1</v>
       </c>
       <c r="I696" s="0" t="n">
-        <v>1</v>
+        <v>17.6058633850347</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29216,10 +29240,10 @@
         <v>2787</v>
       </c>
       <c r="B697" s="0" t="n">
-        <v>-3.12225972222222</v>
+        <v>-3.12229305555555</v>
       </c>
       <c r="C697" s="0" t="n">
-        <v>-41.7651097222223</v>
+        <v>-41.7643652777778</v>
       </c>
       <c r="D697" s="0" t="n">
         <v>77</v>
@@ -29237,7 +29261,7 @@
         <v>1</v>
       </c>
       <c r="I697" s="0" t="n">
-        <v>39.2380095193426</v>
+        <v>17.6085645678712</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29245,10 +29269,10 @@
         <v>2791</v>
       </c>
       <c r="B698" s="0" t="n">
-        <v>-3.12207916666667</v>
+        <v>-3.12243888888889</v>
       </c>
       <c r="C698" s="0" t="n">
-        <v>-41.7651166666666</v>
+        <v>-41.7643208333334</v>
       </c>
       <c r="D698" s="0" t="n">
         <v>77</v>
@@ -29263,7 +29287,7 @@
         <v>2794</v>
       </c>
       <c r="H698" s="0" t="n">
-        <v>24.0743149462092</v>
+        <v>174.256273563526</v>
       </c>
       <c r="I698" s="0" t="n">
         <v>1</v>
@@ -29274,10 +29298,10 @@
         <v>2795</v>
       </c>
       <c r="B699" s="0" t="n">
-        <v>-3.12239861111111</v>
+        <v>-3.12225972222222</v>
       </c>
       <c r="C699" s="0" t="n">
-        <v>-41.7635291666667</v>
+        <v>-41.7651097222223</v>
       </c>
       <c r="D699" s="0" t="n">
         <v>77</v>
@@ -29295,7 +29319,7 @@
         <v>1</v>
       </c>
       <c r="I699" s="0" t="n">
-        <v>8.34532048273702</v>
+        <v>39.2380095193426</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29303,7 +29327,7 @@
         <v>2799</v>
       </c>
       <c r="B700" s="0" t="n">
-        <v>-3.12203333333333</v>
+        <v>-3.12207916666667</v>
       </c>
       <c r="C700" s="0" t="n">
         <v>-41.7651166666666</v>
@@ -29321,7 +29345,7 @@
         <v>2802</v>
       </c>
       <c r="H700" s="0" t="n">
-        <v>23.4477826416907</v>
+        <v>24.0743149462092</v>
       </c>
       <c r="I700" s="0" t="n">
         <v>1</v>
@@ -29332,10 +29356,10 @@
         <v>2803</v>
       </c>
       <c r="B701" s="0" t="n">
-        <v>-3.12329027777778</v>
+        <v>-3.12239861111111</v>
       </c>
       <c r="C701" s="0" t="n">
-        <v>-41.7655361111111</v>
+        <v>-41.7635291666667</v>
       </c>
       <c r="D701" s="0" t="n">
         <v>77</v>
@@ -29350,10 +29374,10 @@
         <v>2806</v>
       </c>
       <c r="H701" s="0" t="n">
-        <v>10.4906918800152</v>
+        <v>1</v>
       </c>
       <c r="I701" s="0" t="n">
-        <v>1</v>
+        <v>8.34532048273702</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29361,10 +29385,10 @@
         <v>2807</v>
       </c>
       <c r="B702" s="0" t="n">
-        <v>-3.12316944444444</v>
+        <v>-3.12203333333333</v>
       </c>
       <c r="C702" s="0" t="n">
-        <v>-41.7655819444444</v>
+        <v>-41.7651166666666</v>
       </c>
       <c r="D702" s="0" t="n">
         <v>77</v>
@@ -29379,10 +29403,10 @@
         <v>2810</v>
       </c>
       <c r="H702" s="0" t="n">
-        <v>1</v>
+        <v>23.4477826416907</v>
       </c>
       <c r="I702" s="0" t="n">
-        <v>26.5650228690678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29393,7 +29417,7 @@
         <v>-3.12329027777778</v>
       </c>
       <c r="C703" s="0" t="n">
-        <v>-41.7651361111111</v>
+        <v>-41.7655361111111</v>
       </c>
       <c r="D703" s="0" t="n">
         <v>77</v>
@@ -29408,7 +29432,7 @@
         <v>2814</v>
       </c>
       <c r="H703" s="0" t="n">
-        <v>35.7775887565438</v>
+        <v>10.4906918800152</v>
       </c>
       <c r="I703" s="0" t="n">
         <v>1</v>
@@ -29419,10 +29443,10 @@
         <v>2815</v>
       </c>
       <c r="B704" s="0" t="n">
-        <v>-3.12295277777778</v>
+        <v>-3.12316944444444</v>
       </c>
       <c r="C704" s="0" t="n">
-        <v>-41.7652194444444</v>
+        <v>-41.7655819444444</v>
       </c>
       <c r="D704" s="0" t="n">
         <v>77</v>
@@ -29440,7 +29464,7 @@
         <v>1</v>
       </c>
       <c r="I704" s="0" t="n">
-        <v>75.3654502815589</v>
+        <v>26.5650228690678</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29448,10 +29472,10 @@
         <v>2819</v>
       </c>
       <c r="B705" s="0" t="n">
-        <v>-3.12314722222222</v>
+        <v>-3.12329027777778</v>
       </c>
       <c r="C705" s="0" t="n">
-        <v>-41.7648569444445</v>
+        <v>-41.7651361111111</v>
       </c>
       <c r="D705" s="0" t="n">
         <v>77</v>
@@ -29466,7 +29490,7 @@
         <v>2822</v>
       </c>
       <c r="H705" s="0" t="n">
-        <v>26.2153631644481</v>
+        <v>35.7775887565438</v>
       </c>
       <c r="I705" s="0" t="n">
         <v>1</v>
@@ -29477,10 +29501,10 @@
         <v>2823</v>
       </c>
       <c r="B706" s="0" t="n">
-        <v>-3.12293611111111</v>
+        <v>-3.12295277777778</v>
       </c>
       <c r="C706" s="0" t="n">
-        <v>-41.7649736111111</v>
+        <v>-41.7652194444444</v>
       </c>
       <c r="D706" s="0" t="n">
         <v>77</v>
@@ -29498,7 +29522,7 @@
         <v>1</v>
       </c>
       <c r="I706" s="0" t="n">
-        <v>85.2500016533164</v>
+        <v>75.3654502815589</v>
       </c>
     </row>
     <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29506,10 +29530,10 @@
         <v>2827</v>
       </c>
       <c r="B707" s="0" t="n">
-        <v>-3.12315</v>
+        <v>-3.12314722222222</v>
       </c>
       <c r="C707" s="0" t="n">
-        <v>-41.7645208333333</v>
+        <v>-41.7648569444445</v>
       </c>
       <c r="D707" s="0" t="n">
         <v>77</v>
@@ -29524,7 +29548,7 @@
         <v>2830</v>
       </c>
       <c r="H707" s="0" t="n">
-        <v>39.1737077318761</v>
+        <v>26.2153631644481</v>
       </c>
       <c r="I707" s="0" t="n">
         <v>1</v>
@@ -29535,10 +29559,10 @@
         <v>2831</v>
       </c>
       <c r="B708" s="0" t="n">
-        <v>-3.12306944444444</v>
+        <v>-3.12293611111111</v>
       </c>
       <c r="C708" s="0" t="n">
-        <v>-41.7646777777778</v>
+        <v>-41.7649736111111</v>
       </c>
       <c r="D708" s="0" t="n">
         <v>77</v>
@@ -29556,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="I708" s="0" t="n">
-        <v>17.9147381814938</v>
+        <v>85.2500016533164</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29567,7 +29591,7 @@
         <v>-3.12315</v>
       </c>
       <c r="C709" s="0" t="n">
-        <v>-41.7642486111112</v>
+        <v>-41.7645208333333</v>
       </c>
       <c r="D709" s="0" t="n">
         <v>77</v>
@@ -29582,7 +29606,7 @@
         <v>2838</v>
       </c>
       <c r="H709" s="0" t="n">
-        <v>12.6450574952605</v>
+        <v>39.1737077318761</v>
       </c>
       <c r="I709" s="0" t="n">
         <v>1</v>
@@ -29593,10 +29617,10 @@
         <v>2839</v>
       </c>
       <c r="B710" s="0" t="n">
-        <v>-3.12281666666666</v>
+        <v>-3.12306944444444</v>
       </c>
       <c r="C710" s="0" t="n">
-        <v>-41.7646763888889</v>
+        <v>-41.7646777777778</v>
       </c>
       <c r="D710" s="0" t="n">
         <v>77</v>
@@ -29614,7 +29638,7 @@
         <v>1</v>
       </c>
       <c r="I710" s="0" t="n">
-        <v>17.9173927965757</v>
+        <v>17.9147381814938</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29622,10 +29646,10 @@
         <v>2843</v>
       </c>
       <c r="B711" s="0" t="n">
-        <v>-3.12289861111111</v>
+        <v>-3.12315</v>
       </c>
       <c r="C711" s="0" t="n">
-        <v>-41.7645111111111</v>
+        <v>-41.7642486111112</v>
       </c>
       <c r="D711" s="0" t="n">
         <v>77</v>
@@ -29640,7 +29664,7 @@
         <v>2846</v>
       </c>
       <c r="H711" s="0" t="n">
-        <v>102.394614467338</v>
+        <v>12.6450574952605</v>
       </c>
       <c r="I711" s="0" t="n">
         <v>1</v>
@@ -29651,10 +29675,10 @@
         <v>2847</v>
       </c>
       <c r="B712" s="0" t="n">
-        <v>-3.12307083333333</v>
+        <v>-3.12281666666666</v>
       </c>
       <c r="C712" s="0" t="n">
-        <v>-41.7643694444445</v>
+        <v>-41.7646763888889</v>
       </c>
       <c r="D712" s="0" t="n">
         <v>77</v>
@@ -29672,7 +29696,7 @@
         <v>1</v>
       </c>
       <c r="I712" s="0" t="n">
-        <v>18.2236129780023</v>
+        <v>17.9173927965757</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29680,10 +29704,10 @@
         <v>2851</v>
       </c>
       <c r="B713" s="0" t="n">
-        <v>-3.1229</v>
+        <v>-3.12289861111111</v>
       </c>
       <c r="C713" s="0" t="n">
-        <v>-41.7637708333334</v>
+        <v>-41.7645111111111</v>
       </c>
       <c r="D713" s="0" t="n">
         <v>77</v>
@@ -29698,7 +29722,7 @@
         <v>2854</v>
       </c>
       <c r="H713" s="0" t="n">
-        <v>51.505490345839</v>
+        <v>102.394614467338</v>
       </c>
       <c r="I713" s="0" t="n">
         <v>1</v>
@@ -29709,10 +29733,10 @@
         <v>2855</v>
       </c>
       <c r="B714" s="0" t="n">
-        <v>-3.12281805555555</v>
+        <v>-3.12307083333333</v>
       </c>
       <c r="C714" s="0" t="n">
-        <v>-41.7643666666667</v>
+        <v>-41.7643694444445</v>
       </c>
       <c r="D714" s="0" t="n">
         <v>77</v>
@@ -29730,7 +29754,7 @@
         <v>1</v>
       </c>
       <c r="I714" s="0" t="n">
-        <v>17.6058633850347</v>
+        <v>18.2236129780023</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29738,10 +29762,10 @@
         <v>2859</v>
       </c>
       <c r="B715" s="0" t="n">
-        <v>-3.12296805555556</v>
+        <v>-3.1229</v>
       </c>
       <c r="C715" s="0" t="n">
-        <v>-41.7658888888889</v>
+        <v>-41.7637708333334</v>
       </c>
       <c r="D715" s="0" t="n">
         <v>77</v>
@@ -29756,7 +29780,7 @@
         <v>2862</v>
       </c>
       <c r="H715" s="0" t="n">
-        <v>41.9457254666118</v>
+        <v>51.505490345839</v>
       </c>
       <c r="I715" s="0" t="n">
         <v>1</v>
@@ -29767,10 +29791,10 @@
         <v>2863</v>
       </c>
       <c r="B716" s="0" t="n">
-        <v>-3.12292916666667</v>
+        <v>-3.12281805555555</v>
       </c>
       <c r="C716" s="0" t="n">
-        <v>-41.7639777777778</v>
+        <v>-41.7643666666667</v>
       </c>
       <c r="D716" s="0" t="n">
         <v>77</v>
@@ -29788,7 +29812,7 @@
         <v>1</v>
       </c>
       <c r="I716" s="0" t="n">
-        <v>44.7868454542777</v>
+        <v>17.6058633850347</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29796,10 +29820,10 @@
         <v>2867</v>
       </c>
       <c r="B717" s="0" t="n">
-        <v>-3.12254861111111</v>
+        <v>-3.12296805555556</v>
       </c>
       <c r="C717" s="0" t="n">
-        <v>-41.7660513888889</v>
+        <v>-41.7658888888889</v>
       </c>
       <c r="D717" s="0" t="n">
         <v>77</v>
@@ -29814,7 +29838,7 @@
         <v>2870</v>
       </c>
       <c r="H717" s="0" t="n">
-        <v>5.25216579986803</v>
+        <v>41.9457254666118</v>
       </c>
       <c r="I717" s="0" t="n">
         <v>1</v>
@@ -29825,10 +29849,10 @@
         <v>2871</v>
       </c>
       <c r="B718" s="0" t="n">
-        <v>-3.12275694444445</v>
+        <v>-3.12292916666667</v>
       </c>
       <c r="C718" s="0" t="n">
-        <v>-41.766075</v>
+        <v>-41.7639777777778</v>
       </c>
       <c r="D718" s="0" t="n">
         <v>77</v>
@@ -29846,7 +29870,7 @@
         <v>1</v>
       </c>
       <c r="I718" s="0" t="n">
-        <v>46.6400942320942</v>
+        <v>44.7868454542777</v>
       </c>
     </row>
     <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29854,10 +29878,10 @@
         <v>2875</v>
       </c>
       <c r="B719" s="0" t="n">
-        <v>-3.12297083333333</v>
+        <v>-3.12254861111111</v>
       </c>
       <c r="C719" s="0" t="n">
-        <v>-41.7656152777778</v>
+        <v>-41.7660513888889</v>
       </c>
       <c r="D719" s="0" t="n">
         <v>77</v>
@@ -29872,7 +29896,7 @@
         <v>2878</v>
       </c>
       <c r="H719" s="0" t="n">
-        <v>7.71658642484199</v>
+        <v>5.25216579986803</v>
       </c>
       <c r="I719" s="0" t="n">
         <v>1</v>
@@ -29883,10 +29907,10 @@
         <v>2879</v>
       </c>
       <c r="B720" s="0" t="n">
-        <v>-3.12298611111111</v>
+        <v>-3.12275694444445</v>
       </c>
       <c r="C720" s="0" t="n">
-        <v>-41.7635958333333</v>
+        <v>-41.766075</v>
       </c>
       <c r="D720" s="0" t="n">
         <v>77</v>
@@ -29904,7 +29928,7 @@
         <v>1</v>
       </c>
       <c r="I720" s="0" t="n">
-        <v>74.1305926721377</v>
+        <v>46.6400942320942</v>
       </c>
     </row>
     <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29912,10 +29936,10 @@
         <v>2883</v>
       </c>
       <c r="B721" s="0" t="n">
-        <v>-3.12370694444444</v>
+        <v>-3.12297083333333</v>
       </c>
       <c r="C721" s="0" t="n">
-        <v>-41.7653430555555</v>
+        <v>-41.7656152777778</v>
       </c>
       <c r="D721" s="0" t="n">
         <v>77</v>
@@ -29930,10 +29954,10 @@
         <v>2886</v>
       </c>
       <c r="H721" s="0" t="n">
-        <v>1</v>
+        <v>7.71658642484199</v>
       </c>
       <c r="I721" s="0" t="n">
-        <v>78.1459320571828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29941,10 +29965,10 @@
         <v>2887</v>
       </c>
       <c r="B722" s="0" t="n">
-        <v>-3.12350277777778</v>
+        <v>-3.12298611111111</v>
       </c>
       <c r="C722" s="0" t="n">
-        <v>-41.7641416666667</v>
+        <v>-41.7635958333333</v>
       </c>
       <c r="D722" s="0" t="n">
         <v>77</v>
@@ -29959,10 +29983,10 @@
         <v>2890</v>
       </c>
       <c r="H722" s="0" t="n">
-        <v>185.050590800252</v>
+        <v>1</v>
       </c>
       <c r="I722" s="0" t="n">
-        <v>1</v>
+        <v>74.1305926721377</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29970,10 +29994,10 @@
         <v>2891</v>
       </c>
       <c r="B723" s="0" t="n">
-        <v>-3.12355416666666</v>
+        <v>-3.12370694444444</v>
       </c>
       <c r="C723" s="0" t="n">
-        <v>-41.7649763888889</v>
+        <v>-41.7653430555555</v>
       </c>
       <c r="D723" s="0" t="n">
         <v>77</v>
@@ -29991,7 +30015,7 @@
         <v>1</v>
       </c>
       <c r="I723" s="0" t="n">
-        <v>44.1701726245875</v>
+        <v>78.1459320571828</v>
       </c>
     </row>
     <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29999,10 +30023,10 @@
         <v>2895</v>
       </c>
       <c r="B724" s="0" t="n">
-        <v>-3.12375277777778</v>
+        <v>-3.12350277777778</v>
       </c>
       <c r="C724" s="0" t="n">
-        <v>-41.7648611111112</v>
+        <v>-41.7641416666667</v>
       </c>
       <c r="D724" s="0" t="n">
         <v>77</v>
@@ -30017,7 +30041,7 @@
         <v>2898</v>
       </c>
       <c r="H724" s="0" t="n">
-        <v>25.9069321832122</v>
+        <v>185.050590800252</v>
       </c>
       <c r="I724" s="0" t="n">
         <v>1</v>
@@ -30028,10 +30052,10 @@
         <v>2899</v>
       </c>
       <c r="B725" s="0" t="n">
-        <v>-3.12384166666666</v>
+        <v>-3.12355416666666</v>
       </c>
       <c r="C725" s="0" t="n">
-        <v>-41.7646805555556</v>
+        <v>-41.7649763888889</v>
       </c>
       <c r="D725" s="0" t="n">
         <v>77</v>
@@ -30049,7 +30073,7 @@
         <v>1</v>
       </c>
       <c r="I725" s="0" t="n">
-        <v>19.1502373674291</v>
+        <v>44.1701726245875</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30057,10 +30081,10 @@
         <v>2903</v>
       </c>
       <c r="B726" s="0" t="n">
-        <v>-3.12375416666666</v>
+        <v>-3.12375277777778</v>
       </c>
       <c r="C726" s="0" t="n">
-        <v>-41.7645277777777</v>
+        <v>-41.7648611111112</v>
       </c>
       <c r="D726" s="0" t="n">
         <v>77</v>
@@ -30075,7 +30099,7 @@
         <v>2906</v>
       </c>
       <c r="H726" s="0" t="n">
-        <v>40.7120650911164</v>
+        <v>25.9069321832122</v>
       </c>
       <c r="I726" s="0" t="n">
         <v>1</v>
@@ -30086,7 +30110,7 @@
         <v>2907</v>
       </c>
       <c r="B727" s="0" t="n">
-        <v>-3.12358888888889</v>
+        <v>-3.12384166666666</v>
       </c>
       <c r="C727" s="0" t="n">
         <v>-41.7646805555556</v>
@@ -30107,7 +30131,7 @@
         <v>1</v>
       </c>
       <c r="I727" s="0" t="n">
-        <v>19.1502373662933</v>
+        <v>19.1502373674291</v>
       </c>
     </row>
     <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30115,10 +30139,10 @@
         <v>2911</v>
       </c>
       <c r="B728" s="0" t="n">
-        <v>-3.12375555555555</v>
+        <v>-3.12375416666666</v>
       </c>
       <c r="C728" s="0" t="n">
-        <v>-41.7641722222222</v>
+        <v>-41.7645277777777</v>
       </c>
       <c r="D728" s="0" t="n">
         <v>77</v>
@@ -30133,7 +30157,7 @@
         <v>2914</v>
       </c>
       <c r="H728" s="0" t="n">
-        <v>30.2247541350932</v>
+        <v>40.7120650911164</v>
       </c>
       <c r="I728" s="0" t="n">
         <v>1</v>
@@ -30144,10 +30168,10 @@
         <v>2915</v>
       </c>
       <c r="B729" s="0" t="n">
-        <v>-3.12384027777777</v>
+        <v>-3.12358888888889</v>
       </c>
       <c r="C729" s="0" t="n">
-        <v>-41.7643708333333</v>
+        <v>-41.7646805555556</v>
       </c>
       <c r="D729" s="0" t="n">
         <v>77</v>
@@ -30165,7 +30189,7 @@
         <v>1</v>
       </c>
       <c r="I729" s="0" t="n">
-        <v>18.8438866439532</v>
+        <v>19.1502373662933</v>
       </c>
     </row>
     <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30173,10 +30197,10 @@
         <v>2919</v>
       </c>
       <c r="B730" s="0" t="n">
-        <v>-3.12375694444444</v>
+        <v>-3.12375555555555</v>
       </c>
       <c r="C730" s="0" t="n">
-        <v>-41.7637680555555</v>
+        <v>-41.7641722222222</v>
       </c>
       <c r="D730" s="0" t="n">
         <v>77</v>
@@ -30191,7 +30215,7 @@
         <v>2922</v>
       </c>
       <c r="H730" s="0" t="n">
-        <v>50.2727337391089</v>
+        <v>30.2247541350932</v>
       </c>
       <c r="I730" s="0" t="n">
         <v>1</v>
@@ -30202,10 +30226,10 @@
         <v>2923</v>
       </c>
       <c r="B731" s="0" t="n">
-        <v>-3.12358888888889</v>
+        <v>-3.12384027777777</v>
       </c>
       <c r="C731" s="0" t="n">
-        <v>-41.7643694444445</v>
+        <v>-41.7643708333333</v>
       </c>
       <c r="D731" s="0" t="n">
         <v>77</v>
@@ -30223,7 +30247,7 @@
         <v>1</v>
       </c>
       <c r="I731" s="0" t="n">
-        <v>19.1502373662933</v>
+        <v>18.8438866439532</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30231,10 +30255,10 @@
         <v>2927</v>
       </c>
       <c r="B732" s="0" t="n">
-        <v>-3.12384027777777</v>
+        <v>-3.12375694444444</v>
       </c>
       <c r="C732" s="0" t="n">
-        <v>-41.7639805555556</v>
+        <v>-41.7637680555555</v>
       </c>
       <c r="D732" s="0" t="n">
         <v>77</v>
@@ -30249,10 +30273,10 @@
         <v>2930</v>
       </c>
       <c r="H732" s="0" t="n">
-        <v>1</v>
+        <v>50.2727337391089</v>
       </c>
       <c r="I732" s="0" t="n">
-        <v>18.2236129780023</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30263,7 +30287,7 @@
         <v>-3.12358888888889</v>
       </c>
       <c r="C733" s="0" t="n">
-        <v>-41.7639916666667</v>
+        <v>-41.7643694444445</v>
       </c>
       <c r="D733" s="0" t="n">
         <v>77</v>
@@ -30289,10 +30313,10 @@
         <v>2935</v>
       </c>
       <c r="B734" s="0" t="n">
-        <v>-3.12353055555555</v>
+        <v>-3.12384027777777</v>
       </c>
       <c r="C734" s="0" t="n">
-        <v>-41.7633069444444</v>
+        <v>-41.7639805555556</v>
       </c>
       <c r="D734" s="0" t="n">
         <v>77</v>
@@ -30310,7 +30334,7 @@
         <v>1</v>
       </c>
       <c r="I734" s="0" t="n">
-        <v>37.0662586828766</v>
+        <v>18.2236129780023</v>
       </c>
     </row>
     <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30318,10 +30342,10 @@
         <v>2939</v>
       </c>
       <c r="B735" s="0" t="n">
-        <v>-3.12343055555556</v>
+        <v>-3.12358888888889</v>
       </c>
       <c r="C735" s="0" t="n">
-        <v>-41.7645638888889</v>
+        <v>-41.7639916666667</v>
       </c>
       <c r="D735" s="0" t="n">
         <v>77</v>
@@ -30336,10 +30360,10 @@
         <v>2942</v>
       </c>
       <c r="H735" s="0" t="n">
-        <v>216.507999723855</v>
+        <v>1</v>
       </c>
       <c r="I735" s="0" t="n">
-        <v>1</v>
+        <v>19.1502373662933</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30347,10 +30371,10 @@
         <v>2943</v>
       </c>
       <c r="B736" s="0" t="n">
-        <v>-3.12373472222222</v>
+        <v>-3.12353055555555</v>
       </c>
       <c r="C736" s="0" t="n">
-        <v>-41.7651069444444</v>
+        <v>-41.7633069444444</v>
       </c>
       <c r="D736" s="0" t="n">
         <v>77</v>
@@ -30368,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="I736" s="0" t="n">
-        <v>65.791054499576</v>
+        <v>37.0662586828766</v>
       </c>
     </row>
     <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30376,10 +30400,10 @@
         <v>2947</v>
       </c>
       <c r="B737" s="0" t="n">
-        <v>-3.12336527777778</v>
+        <v>-3.12343055555556</v>
       </c>
       <c r="C737" s="0" t="n">
-        <v>-41.7634902777778</v>
+        <v>-41.7645638888889</v>
       </c>
       <c r="D737" s="0" t="n">
         <v>77</v>
@@ -30394,7 +30418,7 @@
         <v>2950</v>
       </c>
       <c r="H737" s="0" t="n">
-        <v>19.4326611903087</v>
+        <v>216.507999723855</v>
       </c>
       <c r="I737" s="0" t="n">
         <v>1</v>
@@ -30405,10 +30429,10 @@
         <v>2951</v>
       </c>
       <c r="B738" s="0" t="n">
-        <v>-3.12339861111111</v>
+        <v>-3.12373472222222</v>
       </c>
       <c r="C738" s="0" t="n">
-        <v>-41.7635833333334</v>
+        <v>-41.7651069444444</v>
       </c>
       <c r="D738" s="0" t="n">
         <v>77</v>
@@ -30426,7 +30450,7 @@
         <v>1</v>
       </c>
       <c r="I738" s="0" t="n">
-        <v>7.13084897104345</v>
+        <v>65.791054499576</v>
       </c>
     </row>
     <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30434,10 +30458,10 @@
         <v>2955</v>
       </c>
       <c r="B739" s="0" t="n">
-        <v>-3.12332083333333</v>
+        <v>-3.12336527777778</v>
       </c>
       <c r="C739" s="0" t="n">
-        <v>-41.7634972222223</v>
+        <v>-41.7634902777778</v>
       </c>
       <c r="D739" s="0" t="n">
         <v>77</v>
@@ -30452,7 +30476,7 @@
         <v>2958</v>
       </c>
       <c r="H739" s="0" t="n">
-        <v>20.9745614598014</v>
+        <v>19.4326611903087</v>
       </c>
       <c r="I739" s="0" t="n">
         <v>1</v>
@@ -30463,10 +30487,10 @@
         <v>2959</v>
       </c>
       <c r="B740" s="0" t="n">
-        <v>-3.12403333333333</v>
+        <v>-3.12339861111111</v>
       </c>
       <c r="C740" s="0" t="n">
-        <v>-41.7651236111111</v>
+        <v>-41.7635833333334</v>
       </c>
       <c r="D740" s="0" t="n">
         <v>77</v>
@@ -30481,9 +30505,67 @@
         <v>2962</v>
       </c>
       <c r="H740" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I740" s="0" t="n">
+        <v>7.13084897104345</v>
+      </c>
+    </row>
+    <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A741" s="0" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B741" s="0" t="n">
+        <v>-3.12332083333333</v>
+      </c>
+      <c r="C741" s="0" t="n">
+        <v>-41.7634972222223</v>
+      </c>
+      <c r="D741" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="E741" s="0" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F741" s="0" t="s">
+        <v>2965</v>
+      </c>
+      <c r="G741" s="0" t="s">
+        <v>2966</v>
+      </c>
+      <c r="H741" s="0" t="n">
+        <v>20.9745614598014</v>
+      </c>
+      <c r="I741" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A742" s="0" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B742" s="0" t="n">
+        <v>-3.12403333333333</v>
+      </c>
+      <c r="C742" s="0" t="n">
+        <v>-41.7651236111111</v>
+      </c>
+      <c r="D742" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="E742" s="0" t="s">
+        <v>2968</v>
+      </c>
+      <c r="F742" s="0" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G742" s="0" t="s">
+        <v>2970</v>
+      </c>
+      <c r="H742" s="0" t="n">
         <v>3.39257355102461</v>
       </c>
-      <c r="I740" s="0" t="n">
+      <c r="I742" s="0" t="n">
         <v>1</v>
       </c>
     </row>
